--- a/ProsteNecoNaVic/Excel/01/01_Funkce_KikiZC.xlsx
+++ b/ProsteNecoNaVic/Excel/01/01_Funkce_KikiZC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a - maturita prep\maturita_prep_net\ProsteNecoNaVic\Excel\01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD9732C-442D-4E61-81F9-E48CCCC55E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2E72B3-E434-4AC5-9A78-3B9692027145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2970" windowWidth="29040" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="2970" windowWidth="29040" windowHeight="15960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bankovni_uver" sheetId="3" r:id="rId1"/>
@@ -2306,7 +2306,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;Kč&quot;_-;\-* #,##0.00\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _K_č_-;\-* #,##0.00\ _K_č_-;_-* &quot;-&quot;??\ _K_č_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0\ &quot;Kč&quot;_-;\-* #,##0\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -3112,9 +3112,8 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="1" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="8" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3127,11 +3126,12 @@
     <xf numFmtId="49" fontId="8" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="14" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Čárka 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3142,7 +3142,429 @@
     <cellStyle name="Procenta" xfId="6" builtinId="5"/>
     <cellStyle name="záhlaví" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="44">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4346,18 +4768,18 @@
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D2" s="76"/>
+      <c r="D2" s="70"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="75" t="s">
         <v>718</v>
       </c>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D4" s="64">
@@ -4386,31 +4808,31 @@
       <c r="C5" s="65">
         <v>1000000</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="69">
         <f t="shared" ref="D5:J23" si="0">$C5*(1 + D$4)</f>
         <v>1044999.9999999999</v>
       </c>
-      <c r="E5" s="75">
+      <c r="E5" s="69">
         <f t="shared" ref="E5:J5" si="1">$C5*(1 + E$4)</f>
         <v>1050000</v>
       </c>
-      <c r="F5" s="75">
+      <c r="F5" s="69">
         <f t="shared" si="1"/>
         <v>1055000</v>
       </c>
-      <c r="G5" s="75">
+      <c r="G5" s="69">
         <f t="shared" si="1"/>
         <v>1060000</v>
       </c>
-      <c r="H5" s="75">
+      <c r="H5" s="69">
         <f t="shared" si="1"/>
         <v>1065000</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="69">
         <f t="shared" si="1"/>
         <v>1070000</v>
       </c>
-      <c r="J5" s="75">
+      <c r="J5" s="69">
         <f t="shared" si="1"/>
         <v>1075000</v>
       </c>
@@ -4419,31 +4841,31 @@
       <c r="C6" s="65">
         <v>1500000</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="69">
         <f t="shared" si="0"/>
         <v>1567500</v>
       </c>
-      <c r="E6" s="75">
+      <c r="E6" s="69">
         <f t="shared" si="0"/>
         <v>1575000</v>
       </c>
-      <c r="F6" s="75">
+      <c r="F6" s="69">
         <f t="shared" si="0"/>
         <v>1582500</v>
       </c>
-      <c r="G6" s="75">
+      <c r="G6" s="69">
         <f t="shared" si="0"/>
         <v>1590000</v>
       </c>
-      <c r="H6" s="75">
+      <c r="H6" s="69">
         <f t="shared" si="0"/>
         <v>1597500</v>
       </c>
-      <c r="I6" s="75">
+      <c r="I6" s="69">
         <f t="shared" si="0"/>
         <v>1605000</v>
       </c>
-      <c r="J6" s="75">
+      <c r="J6" s="69">
         <f t="shared" si="0"/>
         <v>1612500</v>
       </c>
@@ -4452,31 +4874,31 @@
       <c r="C7" s="65">
         <v>2000000</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="69">
         <f t="shared" si="0"/>
         <v>2089999.9999999998</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="69">
         <f t="shared" si="0"/>
         <v>2100000</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="69">
         <f t="shared" si="0"/>
         <v>2110000</v>
       </c>
-      <c r="G7" s="75">
+      <c r="G7" s="69">
         <f t="shared" si="0"/>
         <v>2120000</v>
       </c>
-      <c r="H7" s="75">
+      <c r="H7" s="69">
         <f t="shared" si="0"/>
         <v>2130000</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="69">
         <f t="shared" si="0"/>
         <v>2140000</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="69">
         <f t="shared" si="0"/>
         <v>2150000</v>
       </c>
@@ -4485,31 +4907,31 @@
       <c r="C8" s="65">
         <v>2500000</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="69">
         <f t="shared" si="0"/>
         <v>2612500</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="69">
         <f t="shared" si="0"/>
         <v>2625000</v>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="69">
         <f t="shared" si="0"/>
         <v>2637500</v>
       </c>
-      <c r="G8" s="75">
+      <c r="G8" s="69">
         <f t="shared" si="0"/>
         <v>2650000</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="69">
         <f t="shared" si="0"/>
         <v>2662500</v>
       </c>
-      <c r="I8" s="75">
+      <c r="I8" s="69">
         <f t="shared" si="0"/>
         <v>2675000</v>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="69">
         <f t="shared" si="0"/>
         <v>2687500</v>
       </c>
@@ -4518,31 +4940,31 @@
       <c r="C9" s="65">
         <v>3000000</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="69">
         <f t="shared" si="0"/>
         <v>3135000</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="69">
         <f t="shared" si="0"/>
         <v>3150000</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="69">
         <f t="shared" si="0"/>
         <v>3165000</v>
       </c>
-      <c r="G9" s="75">
+      <c r="G9" s="69">
         <f t="shared" si="0"/>
         <v>3180000</v>
       </c>
-      <c r="H9" s="75">
+      <c r="H9" s="69">
         <f t="shared" si="0"/>
         <v>3195000</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="69">
         <f t="shared" si="0"/>
         <v>3210000</v>
       </c>
-      <c r="J9" s="75">
+      <c r="J9" s="69">
         <f t="shared" si="0"/>
         <v>3225000</v>
       </c>
@@ -4551,31 +4973,31 @@
       <c r="C10" s="65">
         <v>3500000</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="69">
         <f t="shared" si="0"/>
         <v>3657499.9999999995</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="69">
         <f t="shared" si="0"/>
         <v>3675000</v>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="69">
         <f t="shared" si="0"/>
         <v>3692500</v>
       </c>
-      <c r="G10" s="75">
+      <c r="G10" s="69">
         <f t="shared" si="0"/>
         <v>3710000</v>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="69">
         <f t="shared" si="0"/>
         <v>3727500</v>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="69">
         <f t="shared" si="0"/>
         <v>3745000</v>
       </c>
-      <c r="J10" s="75">
+      <c r="J10" s="69">
         <f t="shared" si="0"/>
         <v>3762500</v>
       </c>
@@ -4584,31 +5006,31 @@
       <c r="C11" s="65">
         <v>4000000</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="69">
         <f t="shared" si="0"/>
         <v>4179999.9999999995</v>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="69">
         <f t="shared" si="0"/>
         <v>4200000</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="69">
         <f t="shared" si="0"/>
         <v>4220000</v>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="69">
         <f t="shared" si="0"/>
         <v>4240000</v>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="69">
         <f t="shared" si="0"/>
         <v>4260000</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="69">
         <f t="shared" si="0"/>
         <v>4280000</v>
       </c>
-      <c r="J11" s="75">
+      <c r="J11" s="69">
         <f t="shared" si="0"/>
         <v>4300000</v>
       </c>
@@ -4619,31 +5041,31 @@
       <c r="C12" s="65">
         <v>4500000</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="69">
         <f t="shared" si="0"/>
         <v>4702500</v>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="69">
         <f t="shared" si="0"/>
         <v>4725000</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="69">
         <f t="shared" si="0"/>
         <v>4747500</v>
       </c>
-      <c r="G12" s="75">
+      <c r="G12" s="69">
         <f t="shared" si="0"/>
         <v>4770000</v>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="69">
         <f t="shared" si="0"/>
         <v>4792500</v>
       </c>
-      <c r="I12" s="75">
+      <c r="I12" s="69">
         <f t="shared" si="0"/>
         <v>4815000</v>
       </c>
-      <c r="J12" s="75">
+      <c r="J12" s="69">
         <f t="shared" si="0"/>
         <v>4837500</v>
       </c>
@@ -4654,31 +5076,31 @@
       <c r="C13" s="65">
         <v>5000000</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="69">
         <f t="shared" si="0"/>
         <v>5225000</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="69">
         <f t="shared" si="0"/>
         <v>5250000</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="69">
         <f t="shared" si="0"/>
         <v>5275000</v>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="69">
         <f t="shared" si="0"/>
         <v>5300000</v>
       </c>
-      <c r="H13" s="75">
+      <c r="H13" s="69">
         <f t="shared" si="0"/>
         <v>5325000</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="69">
         <f t="shared" si="0"/>
         <v>5350000</v>
       </c>
-      <c r="J13" s="75">
+      <c r="J13" s="69">
         <f t="shared" si="0"/>
         <v>5375000</v>
       </c>
@@ -4687,31 +5109,31 @@
       <c r="C14" s="65">
         <v>5500000</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="69">
         <f t="shared" si="0"/>
         <v>5747500</v>
       </c>
-      <c r="E14" s="75">
+      <c r="E14" s="69">
         <f t="shared" si="0"/>
         <v>5775000</v>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="69">
         <f t="shared" si="0"/>
         <v>5802500</v>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="69">
         <f t="shared" si="0"/>
         <v>5830000</v>
       </c>
-      <c r="H14" s="75">
+      <c r="H14" s="69">
         <f t="shared" si="0"/>
         <v>5857500</v>
       </c>
-      <c r="I14" s="75">
+      <c r="I14" s="69">
         <f t="shared" si="0"/>
         <v>5885000</v>
       </c>
-      <c r="J14" s="75">
+      <c r="J14" s="69">
         <f t="shared" si="0"/>
         <v>5912500</v>
       </c>
@@ -4721,31 +5143,31 @@
       <c r="C15" s="65">
         <v>6000000</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="69">
         <f t="shared" si="0"/>
         <v>6270000</v>
       </c>
-      <c r="E15" s="75">
+      <c r="E15" s="69">
         <f t="shared" si="0"/>
         <v>6300000</v>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="69">
         <f t="shared" si="0"/>
         <v>6330000</v>
       </c>
-      <c r="G15" s="75">
+      <c r="G15" s="69">
         <f t="shared" si="0"/>
         <v>6360000</v>
       </c>
-      <c r="H15" s="75">
+      <c r="H15" s="69">
         <f t="shared" si="0"/>
         <v>6390000</v>
       </c>
-      <c r="I15" s="75">
+      <c r="I15" s="69">
         <f t="shared" si="0"/>
         <v>6420000</v>
       </c>
-      <c r="J15" s="75">
+      <c r="J15" s="69">
         <f t="shared" si="0"/>
         <v>6450000</v>
       </c>
@@ -4755,31 +5177,31 @@
       <c r="C16" s="65">
         <v>6500000</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="69">
         <f t="shared" si="0"/>
         <v>6792500</v>
       </c>
-      <c r="E16" s="75">
+      <c r="E16" s="69">
         <f t="shared" si="0"/>
         <v>6825000</v>
       </c>
-      <c r="F16" s="75">
+      <c r="F16" s="69">
         <f t="shared" si="0"/>
         <v>6857500</v>
       </c>
-      <c r="G16" s="75">
+      <c r="G16" s="69">
         <f t="shared" si="0"/>
         <v>6890000</v>
       </c>
-      <c r="H16" s="75">
+      <c r="H16" s="69">
         <f t="shared" si="0"/>
         <v>6922500</v>
       </c>
-      <c r="I16" s="75">
+      <c r="I16" s="69">
         <f t="shared" si="0"/>
         <v>6955000</v>
       </c>
-      <c r="J16" s="75">
+      <c r="J16" s="69">
         <f t="shared" si="0"/>
         <v>6987500</v>
       </c>
@@ -4788,31 +5210,31 @@
       <c r="C17" s="65">
         <v>7000000</v>
       </c>
-      <c r="D17" s="75">
+      <c r="D17" s="69">
         <f t="shared" si="0"/>
         <v>7314999.9999999991</v>
       </c>
-      <c r="E17" s="75">
+      <c r="E17" s="69">
         <f t="shared" si="0"/>
         <v>7350000</v>
       </c>
-      <c r="F17" s="75">
+      <c r="F17" s="69">
         <f t="shared" si="0"/>
         <v>7385000</v>
       </c>
-      <c r="G17" s="75">
+      <c r="G17" s="69">
         <f t="shared" si="0"/>
         <v>7420000</v>
       </c>
-      <c r="H17" s="75">
+      <c r="H17" s="69">
         <f t="shared" si="0"/>
         <v>7455000</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="69">
         <f t="shared" si="0"/>
         <v>7490000</v>
       </c>
-      <c r="J17" s="75">
+      <c r="J17" s="69">
         <f t="shared" si="0"/>
         <v>7525000</v>
       </c>
@@ -4821,31 +5243,31 @@
       <c r="C18" s="65">
         <v>7500000</v>
       </c>
-      <c r="D18" s="75">
+      <c r="D18" s="69">
         <f t="shared" si="0"/>
         <v>7837499.9999999991</v>
       </c>
-      <c r="E18" s="75">
+      <c r="E18" s="69">
         <f t="shared" si="0"/>
         <v>7875000</v>
       </c>
-      <c r="F18" s="75">
+      <c r="F18" s="69">
         <f t="shared" si="0"/>
         <v>7912499.9999999991</v>
       </c>
-      <c r="G18" s="75">
+      <c r="G18" s="69">
         <f t="shared" si="0"/>
         <v>7950000</v>
       </c>
-      <c r="H18" s="75">
+      <c r="H18" s="69">
         <f t="shared" si="0"/>
         <v>7987500</v>
       </c>
-      <c r="I18" s="75">
+      <c r="I18" s="69">
         <f t="shared" si="0"/>
         <v>8025000.0000000009</v>
       </c>
-      <c r="J18" s="75">
+      <c r="J18" s="69">
         <f t="shared" si="0"/>
         <v>8062500</v>
       </c>
@@ -4854,31 +5276,31 @@
       <c r="C19" s="65">
         <v>8000000</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19" s="69">
         <f t="shared" si="0"/>
         <v>8359999.9999999991</v>
       </c>
-      <c r="E19" s="75">
+      <c r="E19" s="69">
         <f t="shared" si="0"/>
         <v>8400000</v>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="69">
         <f t="shared" si="0"/>
         <v>8440000</v>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="69">
         <f t="shared" si="0"/>
         <v>8480000</v>
       </c>
-      <c r="H19" s="75">
+      <c r="H19" s="69">
         <f t="shared" si="0"/>
         <v>8520000</v>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="69">
         <f t="shared" si="0"/>
         <v>8560000</v>
       </c>
-      <c r="J19" s="75">
+      <c r="J19" s="69">
         <f t="shared" si="0"/>
         <v>8600000</v>
       </c>
@@ -4888,31 +5310,31 @@
       <c r="C20" s="65">
         <v>8500000</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D20" s="69">
         <f t="shared" si="0"/>
         <v>8882500</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="69">
         <f t="shared" si="0"/>
         <v>8925000</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="69">
         <f t="shared" si="0"/>
         <v>8967500</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="69">
         <f t="shared" si="0"/>
         <v>9010000</v>
       </c>
-      <c r="H20" s="75">
+      <c r="H20" s="69">
         <f t="shared" si="0"/>
         <v>9052500</v>
       </c>
-      <c r="I20" s="75">
+      <c r="I20" s="69">
         <f t="shared" si="0"/>
         <v>9095000</v>
       </c>
-      <c r="J20" s="75">
+      <c r="J20" s="69">
         <f t="shared" si="0"/>
         <v>9137500</v>
       </c>
@@ -4921,31 +5343,31 @@
       <c r="C21" s="65">
         <v>9000000</v>
       </c>
-      <c r="D21" s="75">
+      <c r="D21" s="69">
         <f t="shared" si="0"/>
         <v>9405000</v>
       </c>
-      <c r="E21" s="75">
+      <c r="E21" s="69">
         <f t="shared" si="0"/>
         <v>9450000</v>
       </c>
-      <c r="F21" s="75">
+      <c r="F21" s="69">
         <f t="shared" si="0"/>
         <v>9495000</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="69">
         <f t="shared" si="0"/>
         <v>9540000</v>
       </c>
-      <c r="H21" s="75">
+      <c r="H21" s="69">
         <f t="shared" si="0"/>
         <v>9585000</v>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="69">
         <f t="shared" si="0"/>
         <v>9630000</v>
       </c>
-      <c r="J21" s="75">
+      <c r="J21" s="69">
         <f t="shared" si="0"/>
         <v>9675000</v>
       </c>
@@ -4954,31 +5376,31 @@
       <c r="C22" s="65">
         <v>9500000</v>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="69">
         <f t="shared" si="0"/>
         <v>9927500</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="69">
         <f t="shared" si="0"/>
         <v>9975000</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F22" s="69">
         <f t="shared" si="0"/>
         <v>10022500</v>
       </c>
-      <c r="G22" s="75">
+      <c r="G22" s="69">
         <f t="shared" si="0"/>
         <v>10070000</v>
       </c>
-      <c r="H22" s="75">
+      <c r="H22" s="69">
         <f t="shared" si="0"/>
         <v>10117500</v>
       </c>
-      <c r="I22" s="75">
+      <c r="I22" s="69">
         <f t="shared" si="0"/>
         <v>10165000</v>
       </c>
-      <c r="J22" s="75">
+      <c r="J22" s="69">
         <f t="shared" si="0"/>
         <v>10212500</v>
       </c>
@@ -4987,31 +5409,31 @@
       <c r="C23" s="65">
         <v>10000000</v>
       </c>
-      <c r="D23" s="75">
+      <c r="D23" s="69">
         <f t="shared" si="0"/>
         <v>10450000</v>
       </c>
-      <c r="E23" s="75">
+      <c r="E23" s="69">
         <f t="shared" si="0"/>
         <v>10500000</v>
       </c>
-      <c r="F23" s="75">
+      <c r="F23" s="69">
         <f t="shared" si="0"/>
         <v>10550000</v>
       </c>
-      <c r="G23" s="75">
+      <c r="G23" s="69">
         <f t="shared" si="0"/>
         <v>10600000</v>
       </c>
-      <c r="H23" s="75">
+      <c r="H23" s="69">
         <f t="shared" si="0"/>
         <v>10650000</v>
       </c>
-      <c r="I23" s="75">
+      <c r="I23" s="69">
         <f t="shared" si="0"/>
         <v>10700000</v>
       </c>
-      <c r="J23" s="75">
+      <c r="J23" s="69">
         <f t="shared" si="0"/>
         <v>10750000</v>
       </c>
@@ -5138,40 +5560,40 @@
       <c r="A10" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="72"/>
     </row>
     <row r="11" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="74"/>
     </row>
     <row r="12" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="74"/>
     </row>
     <row r="13" spans="1:7" ht="26.45" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -5185,7 +5607,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="25">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
@@ -5209,8 +5631,8 @@
         <v>20</v>
       </c>
       <c r="C19" s="29">
-        <f>C16*C17</f>
-        <v>90</v>
+        <f>C16*C17+C18</f>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
@@ -5249,6 +5671,21 @@
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="B12:G12"/>
   </mergeCells>
+  <conditionalFormatting sqref="C3:E5">
+    <cfRule type="top10" dxfId="5" priority="3" rank="1"/>
+    <cfRule type="aboveAverage" dxfId="4" priority="4"/>
+    <cfRule type="top10" dxfId="3" priority="5" bottom="1" rank="1"/>
+    <cfRule type="top10" dxfId="2" priority="6" rank="1"/>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="between">
+      <formula>$C$7</formula>
+      <formula>$C$8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$C$16*$C$17+$C$18&lt;100</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -8266,10 +8703,10 @@
       <c r="E65" s="60"/>
     </row>
     <row r="67" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D67" s="74" t="s">
+      <c r="D67" s="76" t="s">
         <v>719</v>
       </c>
-      <c r="E67" s="74"/>
+      <c r="E67" s="76"/>
     </row>
     <row r="68" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D68" s="63" t="s">
@@ -8364,7 +8801,7 @@
       </c>
       <c r="E5" s="41">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="46">
         <v>43023</v>
@@ -8391,7 +8828,7 @@
       </c>
       <c r="E6" s="41">
         <f t="shared" ref="E6:E69" ca="1" si="0">RANDBETWEEN(1,20)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F6" s="46">
         <v>43191</v>
@@ -8419,7 +8856,7 @@
       </c>
       <c r="E7" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F7" s="46">
         <v>43370</v>
@@ -8440,7 +8877,7 @@
       </c>
       <c r="E8" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F8" s="46">
         <v>43384</v>
@@ -8461,7 +8898,7 @@
       </c>
       <c r="E9" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F9" s="46">
         <v>43383</v>
@@ -8482,7 +8919,7 @@
       </c>
       <c r="E10" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" s="46">
         <v>43380</v>
@@ -8503,7 +8940,7 @@
       </c>
       <c r="E11" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F11" s="46">
         <v>43385</v>
@@ -8524,7 +8961,7 @@
       </c>
       <c r="E12" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F12" s="46">
         <v>43369</v>
@@ -8545,7 +8982,7 @@
       </c>
       <c r="E13" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F13" s="46">
         <v>43372</v>
@@ -8566,7 +9003,7 @@
       </c>
       <c r="E14" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F14" s="46">
         <v>43369</v>
@@ -8587,7 +9024,7 @@
       </c>
       <c r="E15" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F15" s="46">
         <v>43375</v>
@@ -8608,7 +9045,7 @@
       </c>
       <c r="E16" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F16" s="46">
         <v>43379</v>
@@ -8629,7 +9066,7 @@
       </c>
       <c r="E17" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F17" s="46">
         <v>43374</v>
@@ -8650,7 +9087,7 @@
       </c>
       <c r="E18" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="46">
         <v>43372</v>
@@ -8671,7 +9108,7 @@
       </c>
       <c r="E19" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19" s="46">
         <v>43370</v>
@@ -8692,7 +9129,7 @@
       </c>
       <c r="E20" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F20" s="46">
         <v>43373</v>
@@ -8713,7 +9150,7 @@
       </c>
       <c r="E21" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F21" s="46">
         <v>43375</v>
@@ -8734,7 +9171,7 @@
       </c>
       <c r="E22" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F22" s="46">
         <v>43373</v>
@@ -8755,7 +9192,7 @@
       </c>
       <c r="E23" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F23" s="46">
         <v>43378</v>
@@ -8776,7 +9213,7 @@
       </c>
       <c r="E24" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F24" s="46">
         <v>43388</v>
@@ -8797,7 +9234,7 @@
       </c>
       <c r="E25" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F25" s="46">
         <v>43380</v>
@@ -8818,7 +9255,7 @@
       </c>
       <c r="E26" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" s="46">
         <v>43379</v>
@@ -8839,7 +9276,7 @@
       </c>
       <c r="E27" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F27" s="46">
         <v>43380</v>
@@ -8860,7 +9297,7 @@
       </c>
       <c r="E28" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F28" s="46">
         <v>43377</v>
@@ -8881,7 +9318,7 @@
       </c>
       <c r="E29" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" s="46">
         <v>43380</v>
@@ -8902,7 +9339,7 @@
       </c>
       <c r="E30" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F30" s="46">
         <v>43369</v>
@@ -8923,7 +9360,7 @@
       </c>
       <c r="E31" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F31" s="46">
         <v>43369</v>
@@ -8944,7 +9381,7 @@
       </c>
       <c r="E32" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F32" s="46">
         <v>43385</v>
@@ -8965,7 +9402,7 @@
       </c>
       <c r="E33" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F33" s="46">
         <v>43387</v>
@@ -8986,7 +9423,7 @@
       </c>
       <c r="E34" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F34" s="46">
         <v>43371</v>
@@ -9007,7 +9444,7 @@
       </c>
       <c r="E35" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F35" s="46">
         <v>43375</v>
@@ -9028,7 +9465,7 @@
       </c>
       <c r="E36" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="46">
         <v>43373</v>
@@ -9049,7 +9486,7 @@
       </c>
       <c r="E37" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F37" s="46">
         <v>43380</v>
@@ -9070,7 +9507,7 @@
       </c>
       <c r="E38" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F38" s="46">
         <v>43381</v>
@@ -9091,7 +9528,7 @@
       </c>
       <c r="E39" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F39" s="46">
         <v>43384</v>
@@ -9112,7 +9549,7 @@
       </c>
       <c r="E40" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F40" s="46">
         <v>43386</v>
@@ -9133,7 +9570,7 @@
       </c>
       <c r="E41" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F41" s="46">
         <v>43380</v>
@@ -9154,7 +9591,7 @@
       </c>
       <c r="E42" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F42" s="46">
         <v>43387</v>
@@ -9175,7 +9612,7 @@
       </c>
       <c r="E43" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F43" s="46">
         <v>43380</v>
@@ -9196,7 +9633,7 @@
       </c>
       <c r="E44" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F44" s="46">
         <v>43382</v>
@@ -9217,7 +9654,7 @@
       </c>
       <c r="E45" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F45" s="46">
         <v>43373</v>
@@ -9238,7 +9675,7 @@
       </c>
       <c r="E46" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F46" s="46">
         <v>43376</v>
@@ -9259,7 +9696,7 @@
       </c>
       <c r="E47" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F47" s="46">
         <v>43386</v>
@@ -9280,7 +9717,7 @@
       </c>
       <c r="E48" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F48" s="46">
         <v>43383</v>
@@ -9301,7 +9738,7 @@
       </c>
       <c r="E49" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F49" s="46">
         <v>43384</v>
@@ -9322,7 +9759,7 @@
       </c>
       <c r="E50" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F50" s="46">
         <v>43373</v>
@@ -9343,7 +9780,7 @@
       </c>
       <c r="E51" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F51" s="46">
         <v>43380</v>
@@ -9364,7 +9801,7 @@
       </c>
       <c r="E52" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F52" s="46">
         <v>43387</v>
@@ -9385,7 +9822,7 @@
       </c>
       <c r="E53" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F53" s="46">
         <v>43375</v>
@@ -9406,7 +9843,7 @@
       </c>
       <c r="E54" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54" s="46">
         <v>43371</v>
@@ -9427,7 +9864,7 @@
       </c>
       <c r="E55" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F55" s="46">
         <v>43371</v>
@@ -9448,7 +9885,7 @@
       </c>
       <c r="E56" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F56" s="46">
         <v>43378</v>
@@ -9490,7 +9927,7 @@
       </c>
       <c r="E58" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F58" s="46">
         <v>43375</v>
@@ -9511,7 +9948,7 @@
       </c>
       <c r="E59" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F59" s="46">
         <v>43378</v>
@@ -9532,7 +9969,7 @@
       </c>
       <c r="E60" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F60" s="46">
         <v>43384</v>
@@ -9553,7 +9990,7 @@
       </c>
       <c r="E61" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F61" s="46">
         <v>43382</v>
@@ -9574,7 +10011,7 @@
       </c>
       <c r="E62" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F62" s="46">
         <v>43383</v>
@@ -9595,7 +10032,7 @@
       </c>
       <c r="E63" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F63" s="46">
         <v>43381</v>
@@ -9616,7 +10053,7 @@
       </c>
       <c r="E64" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F64" s="46">
         <v>43372</v>
@@ -9637,7 +10074,7 @@
       </c>
       <c r="E65" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F65" s="46">
         <v>43376</v>
@@ -9658,7 +10095,7 @@
       </c>
       <c r="E66" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F66" s="46">
         <v>43371</v>
@@ -9679,7 +10116,7 @@
       </c>
       <c r="E67" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F67" s="46">
         <v>43375</v>
@@ -9700,7 +10137,7 @@
       </c>
       <c r="E68" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F68" s="46">
         <v>43370</v>
@@ -9721,7 +10158,7 @@
       </c>
       <c r="E69" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F69" s="46">
         <v>43374</v>
@@ -9742,7 +10179,7 @@
       </c>
       <c r="E70" s="41">
         <f t="shared" ref="E70:E133" ca="1" si="1">RANDBETWEEN(1,20)</f>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F70" s="46">
         <v>43371</v>
@@ -9763,7 +10200,7 @@
       </c>
       <c r="E71" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F71" s="46">
         <v>43380</v>
@@ -9784,7 +10221,7 @@
       </c>
       <c r="E72" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F72" s="46">
         <v>43374</v>
@@ -9805,7 +10242,7 @@
       </c>
       <c r="E73" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F73" s="46">
         <v>43387</v>
@@ -9826,7 +10263,7 @@
       </c>
       <c r="E74" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F74" s="46">
         <v>43374</v>
@@ -9847,7 +10284,7 @@
       </c>
       <c r="E75" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F75" s="46">
         <v>43374</v>
@@ -9868,7 +10305,7 @@
       </c>
       <c r="E76" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F76" s="46">
         <v>43371</v>
@@ -9889,7 +10326,7 @@
       </c>
       <c r="E77" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F77" s="46">
         <v>43374</v>
@@ -9910,7 +10347,7 @@
       </c>
       <c r="E78" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F78" s="46">
         <v>43388</v>
@@ -9931,7 +10368,7 @@
       </c>
       <c r="E79" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F79" s="46">
         <v>43381</v>
@@ -9952,7 +10389,7 @@
       </c>
       <c r="E80" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F80" s="46">
         <v>43378</v>
@@ -9973,7 +10410,7 @@
       </c>
       <c r="E81" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F81" s="46">
         <v>43384</v>
@@ -9994,7 +10431,7 @@
       </c>
       <c r="E82" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F82" s="46">
         <v>43370</v>
@@ -10015,7 +10452,7 @@
       </c>
       <c r="E83" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F83" s="46">
         <v>43375</v>
@@ -10036,7 +10473,7 @@
       </c>
       <c r="E84" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F84" s="46">
         <v>43386</v>
@@ -10057,7 +10494,7 @@
       </c>
       <c r="E85" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F85" s="46">
         <v>43381</v>
@@ -10078,7 +10515,7 @@
       </c>
       <c r="E86" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F86" s="46">
         <v>43383</v>
@@ -10099,7 +10536,7 @@
       </c>
       <c r="E87" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F87" s="46">
         <v>43379</v>
@@ -10120,7 +10557,7 @@
       </c>
       <c r="E88" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F88" s="46">
         <v>43376</v>
@@ -10141,7 +10578,7 @@
       </c>
       <c r="E89" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F89" s="46">
         <v>43370</v>
@@ -10162,7 +10599,7 @@
       </c>
       <c r="E90" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F90" s="46">
         <v>43383</v>
@@ -10204,7 +10641,7 @@
       </c>
       <c r="E92" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F92" s="46">
         <v>43388</v>
@@ -10225,7 +10662,7 @@
       </c>
       <c r="E93" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F93" s="46">
         <v>43380</v>
@@ -10246,7 +10683,7 @@
       </c>
       <c r="E94" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F94" s="46">
         <v>43376</v>
@@ -10267,7 +10704,7 @@
       </c>
       <c r="E95" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F95" s="46">
         <v>43372</v>
@@ -10288,7 +10725,7 @@
       </c>
       <c r="E96" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F96" s="46">
         <v>43375</v>
@@ -10309,7 +10746,7 @@
       </c>
       <c r="E97" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F97" s="46">
         <v>43369</v>
@@ -10330,7 +10767,7 @@
       </c>
       <c r="E98" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F98" s="46">
         <v>43375</v>
@@ -10351,7 +10788,7 @@
       </c>
       <c r="E99" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F99" s="46">
         <v>43372</v>
@@ -10372,7 +10809,7 @@
       </c>
       <c r="E100" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F100" s="46">
         <v>43388</v>
@@ -10393,7 +10830,7 @@
       </c>
       <c r="E101" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F101" s="46">
         <v>43373</v>
@@ -10414,7 +10851,7 @@
       </c>
       <c r="E102" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F102" s="46">
         <v>43375</v>
@@ -10435,7 +10872,7 @@
       </c>
       <c r="E103" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F103" s="46">
         <v>43376</v>
@@ -10456,7 +10893,7 @@
       </c>
       <c r="E104" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F104" s="46">
         <v>43384</v>
@@ -10477,7 +10914,7 @@
       </c>
       <c r="E105" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F105" s="46">
         <v>43371</v>
@@ -10498,7 +10935,7 @@
       </c>
       <c r="E106" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F106" s="46">
         <v>43375</v>
@@ -10519,7 +10956,7 @@
       </c>
       <c r="E107" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F107" s="46">
         <v>43386</v>
@@ -10561,7 +10998,7 @@
       </c>
       <c r="E109" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F109" s="46">
         <v>43379</v>
@@ -10582,7 +11019,7 @@
       </c>
       <c r="E110" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="46">
         <v>43382</v>
@@ -10603,7 +11040,7 @@
       </c>
       <c r="E111" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F111" s="46">
         <v>43379</v>
@@ -10624,7 +11061,7 @@
       </c>
       <c r="E112" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F112" s="46">
         <v>43384</v>
@@ -10645,7 +11082,7 @@
       </c>
       <c r="E113" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F113" s="46">
         <v>43377</v>
@@ -10666,7 +11103,7 @@
       </c>
       <c r="E114" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F114" s="46">
         <v>43385</v>
@@ -10687,7 +11124,7 @@
       </c>
       <c r="E115" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F115" s="46">
         <v>43378</v>
@@ -10708,7 +11145,7 @@
       </c>
       <c r="E116" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F116" s="46">
         <v>43375</v>
@@ -10729,7 +11166,7 @@
       </c>
       <c r="E117" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F117" s="46">
         <v>43376</v>
@@ -10750,7 +11187,7 @@
       </c>
       <c r="E118" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F118" s="46">
         <v>43385</v>
@@ -10771,7 +11208,7 @@
       </c>
       <c r="E119" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F119" s="46">
         <v>43382</v>
@@ -10792,7 +11229,7 @@
       </c>
       <c r="E120" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F120" s="46">
         <v>43387</v>
@@ -10813,7 +11250,7 @@
       </c>
       <c r="E121" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F121" s="46">
         <v>43386</v>
@@ -10834,7 +11271,7 @@
       </c>
       <c r="E122" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F122" s="46">
         <v>43381</v>
@@ -10855,7 +11292,7 @@
       </c>
       <c r="E123" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F123" s="46">
         <v>43374</v>
@@ -10876,7 +11313,7 @@
       </c>
       <c r="E124" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F124" s="46">
         <v>43386</v>
@@ -10897,7 +11334,7 @@
       </c>
       <c r="E125" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F125" s="46">
         <v>43374</v>
@@ -10918,7 +11355,7 @@
       </c>
       <c r="E126" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F126" s="46">
         <v>43383</v>
@@ -10939,7 +11376,7 @@
       </c>
       <c r="E127" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F127" s="46">
         <v>43382</v>
@@ -10960,7 +11397,7 @@
       </c>
       <c r="E128" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F128" s="46">
         <v>43371</v>
@@ -10981,7 +11418,7 @@
       </c>
       <c r="E129" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F129" s="46">
         <v>43369</v>
@@ -11002,7 +11439,7 @@
       </c>
       <c r="E130" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F130" s="46">
         <v>43378</v>
@@ -11023,7 +11460,7 @@
       </c>
       <c r="E131" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F131" s="46">
         <v>43373</v>
@@ -11044,7 +11481,7 @@
       </c>
       <c r="E132" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F132" s="46">
         <v>43369</v>
@@ -11065,7 +11502,7 @@
       </c>
       <c r="E133" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F133" s="46">
         <v>43373</v>
@@ -11086,7 +11523,7 @@
       </c>
       <c r="E134" s="41">
         <f t="shared" ref="E134:E197" ca="1" si="2">RANDBETWEEN(1,20)</f>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F134" s="46">
         <v>43388</v>
@@ -11107,7 +11544,7 @@
       </c>
       <c r="E135" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F135" s="46">
         <v>43370</v>
@@ -11128,7 +11565,7 @@
       </c>
       <c r="E136" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F136" s="46">
         <v>43374</v>
@@ -11149,7 +11586,7 @@
       </c>
       <c r="E137" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F137" s="46">
         <v>43380</v>
@@ -11170,7 +11607,7 @@
       </c>
       <c r="E138" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F138" s="46">
         <v>43381</v>
@@ -11191,7 +11628,7 @@
       </c>
       <c r="E139" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F139" s="46">
         <v>43382</v>
@@ -11212,7 +11649,7 @@
       </c>
       <c r="E140" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F140" s="46">
         <v>43375</v>
@@ -11233,7 +11670,7 @@
       </c>
       <c r="E141" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F141" s="46">
         <v>43380</v>
@@ -11254,7 +11691,7 @@
       </c>
       <c r="E142" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F142" s="46">
         <v>43381</v>
@@ -11275,7 +11712,7 @@
       </c>
       <c r="E143" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F143" s="46">
         <v>43383</v>
@@ -11296,7 +11733,7 @@
       </c>
       <c r="E144" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F144" s="46">
         <v>43371</v>
@@ -11317,7 +11754,7 @@
       </c>
       <c r="E145" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F145" s="46">
         <v>43375</v>
@@ -11338,7 +11775,7 @@
       </c>
       <c r="E146" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F146" s="46">
         <v>43373</v>
@@ -11359,7 +11796,7 @@
       </c>
       <c r="E147" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F147" s="46">
         <v>43386</v>
@@ -11380,7 +11817,7 @@
       </c>
       <c r="E148" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F148" s="46">
         <v>43377</v>
@@ -11401,7 +11838,7 @@
       </c>
       <c r="E149" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F149" s="46">
         <v>43380</v>
@@ -11443,7 +11880,7 @@
       </c>
       <c r="E151" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F151" s="46">
         <v>43369</v>
@@ -11464,7 +11901,7 @@
       </c>
       <c r="E152" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F152" s="46">
         <v>43369</v>
@@ -11506,7 +11943,7 @@
       </c>
       <c r="E154" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F154" s="46">
         <v>43376</v>
@@ -11527,7 +11964,7 @@
       </c>
       <c r="E155" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F155" s="46">
         <v>43383</v>
@@ -11548,7 +11985,7 @@
       </c>
       <c r="E156" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F156" s="46">
         <v>43372</v>
@@ -11569,7 +12006,7 @@
       </c>
       <c r="E157" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F157" s="46">
         <v>43371</v>
@@ -11590,7 +12027,7 @@
       </c>
       <c r="E158" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F158" s="46">
         <v>43370</v>
@@ -11611,7 +12048,7 @@
       </c>
       <c r="E159" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F159" s="46">
         <v>43380</v>
@@ -11632,7 +12069,7 @@
       </c>
       <c r="E160" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F160" s="46">
         <v>43381</v>
@@ -11653,7 +12090,7 @@
       </c>
       <c r="E161" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F161" s="46">
         <v>43377</v>
@@ -11674,7 +12111,7 @@
       </c>
       <c r="E162" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F162" s="46">
         <v>43375</v>
@@ -11695,7 +12132,7 @@
       </c>
       <c r="E163" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F163" s="46">
         <v>43372</v>
@@ -11716,7 +12153,7 @@
       </c>
       <c r="E164" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F164" s="46">
         <v>43383</v>
@@ -11737,7 +12174,7 @@
       </c>
       <c r="E165" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F165" s="46">
         <v>43380</v>
@@ -11758,7 +12195,7 @@
       </c>
       <c r="E166" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F166" s="46">
         <v>43383</v>
@@ -11779,7 +12216,7 @@
       </c>
       <c r="E167" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F167" s="46">
         <v>43374</v>
@@ -11800,7 +12237,7 @@
       </c>
       <c r="E168" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F168" s="46">
         <v>43385</v>
@@ -11821,7 +12258,7 @@
       </c>
       <c r="E169" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F169" s="46">
         <v>43388</v>
@@ -11863,7 +12300,7 @@
       </c>
       <c r="E171" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F171" s="46">
         <v>43380</v>
@@ -11884,7 +12321,7 @@
       </c>
       <c r="E172" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F172" s="46">
         <v>43384</v>
@@ -11905,7 +12342,7 @@
       </c>
       <c r="E173" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F173" s="46">
         <v>43371</v>
@@ -11926,7 +12363,7 @@
       </c>
       <c r="E174" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F174" s="46">
         <v>43383</v>
@@ -11947,7 +12384,7 @@
       </c>
       <c r="E175" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F175" s="46">
         <v>43370</v>
@@ -11968,7 +12405,7 @@
       </c>
       <c r="E176" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F176" s="46">
         <v>43372</v>
@@ -11989,7 +12426,7 @@
       </c>
       <c r="E177" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F177" s="46">
         <v>43378</v>
@@ -12010,7 +12447,7 @@
       </c>
       <c r="E178" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F178" s="46">
         <v>43373</v>
@@ -12031,7 +12468,7 @@
       </c>
       <c r="E179" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F179" s="46">
         <v>43375</v>
@@ -12052,7 +12489,7 @@
       </c>
       <c r="E180" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F180" s="46">
         <v>43382</v>
@@ -12073,7 +12510,7 @@
       </c>
       <c r="E181" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F181" s="46">
         <v>43371</v>
@@ -12094,7 +12531,7 @@
       </c>
       <c r="E182" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F182" s="46">
         <v>43375</v>
@@ -12115,7 +12552,7 @@
       </c>
       <c r="E183" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F183" s="46">
         <v>43373</v>
@@ -12136,7 +12573,7 @@
       </c>
       <c r="E184" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F184" s="46">
         <v>43379</v>
@@ -12157,7 +12594,7 @@
       </c>
       <c r="E185" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F185" s="46">
         <v>43372</v>
@@ -12199,7 +12636,7 @@
       </c>
       <c r="E187" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F187" s="46">
         <v>43379</v>
@@ -12220,7 +12657,7 @@
       </c>
       <c r="E188" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F188" s="46">
         <v>43372</v>
@@ -12241,7 +12678,7 @@
       </c>
       <c r="E189" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F189" s="46">
         <v>43384</v>
@@ -12262,7 +12699,7 @@
       </c>
       <c r="E190" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F190" s="46">
         <v>43370</v>
@@ -12283,7 +12720,7 @@
       </c>
       <c r="E191" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F191" s="46">
         <v>43378</v>
@@ -12325,7 +12762,7 @@
       </c>
       <c r="E193" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F193" s="46">
         <v>43373</v>
@@ -12346,7 +12783,7 @@
       </c>
       <c r="E194" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F194" s="46">
         <v>43372</v>
@@ -12367,7 +12804,7 @@
       </c>
       <c r="E195" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F195" s="46">
         <v>43379</v>
@@ -12388,7 +12825,7 @@
       </c>
       <c r="E196" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F196" s="46">
         <v>43382</v>
@@ -12409,7 +12846,7 @@
       </c>
       <c r="E197" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F197" s="46">
         <v>43386</v>
@@ -12430,7 +12867,7 @@
       </c>
       <c r="E198" s="41">
         <f t="shared" ref="E198:E261" ca="1" si="3">RANDBETWEEN(1,20)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F198" s="46">
         <v>43375</v>
@@ -12451,7 +12888,7 @@
       </c>
       <c r="E199" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F199" s="46">
         <v>43375</v>
@@ -12472,7 +12909,7 @@
       </c>
       <c r="E200" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F200" s="46">
         <v>43372</v>
@@ -12514,7 +12951,7 @@
       </c>
       <c r="E202" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F202" s="46">
         <v>43386</v>
@@ -12535,7 +12972,7 @@
       </c>
       <c r="E203" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F203" s="46">
         <v>43380</v>
@@ -12556,7 +12993,7 @@
       </c>
       <c r="E204" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F204" s="46">
         <v>43377</v>
@@ -12577,7 +13014,7 @@
       </c>
       <c r="E205" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F205" s="46">
         <v>43380</v>
@@ -12598,7 +13035,7 @@
       </c>
       <c r="E206" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F206" s="46">
         <v>43380</v>
@@ -12619,7 +13056,7 @@
       </c>
       <c r="E207" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F207" s="46">
         <v>43371</v>
@@ -12640,7 +13077,7 @@
       </c>
       <c r="E208" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F208" s="46">
         <v>43385</v>
@@ -12661,7 +13098,7 @@
       </c>
       <c r="E209" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F209" s="46">
         <v>43371</v>
@@ -12682,7 +13119,7 @@
       </c>
       <c r="E210" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F210" s="46">
         <v>43371</v>
@@ -12703,7 +13140,7 @@
       </c>
       <c r="E211" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F211" s="46">
         <v>43383</v>
@@ -12724,7 +13161,7 @@
       </c>
       <c r="E212" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F212" s="46">
         <v>43378</v>
@@ -12745,7 +13182,7 @@
       </c>
       <c r="E213" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F213" s="46">
         <v>43379</v>
@@ -12766,7 +13203,7 @@
       </c>
       <c r="E214" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F214" s="46">
         <v>43383</v>
@@ -12787,7 +13224,7 @@
       </c>
       <c r="E215" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F215" s="46">
         <v>43381</v>
@@ -12808,7 +13245,7 @@
       </c>
       <c r="E216" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F216" s="46">
         <v>43369</v>
@@ -12829,7 +13266,7 @@
       </c>
       <c r="E217" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F217" s="46">
         <v>43375</v>
@@ -12850,7 +13287,7 @@
       </c>
       <c r="E218" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F218" s="46">
         <v>43376</v>
@@ -12871,7 +13308,7 @@
       </c>
       <c r="E219" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F219" s="46">
         <v>43371</v>
@@ -12892,7 +13329,7 @@
       </c>
       <c r="E220" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F220" s="46">
         <v>43379</v>
@@ -12913,7 +13350,7 @@
       </c>
       <c r="E221" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F221" s="46">
         <v>43384</v>
@@ -12934,7 +13371,7 @@
       </c>
       <c r="E222" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F222" s="46">
         <v>43384</v>
@@ -12955,7 +13392,7 @@
       </c>
       <c r="E223" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F223" s="46">
         <v>43380</v>
@@ -12976,7 +13413,7 @@
       </c>
       <c r="E224" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F224" s="46">
         <v>43382</v>
@@ -12997,7 +13434,7 @@
       </c>
       <c r="E225" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F225" s="46">
         <v>43381</v>
@@ -13018,7 +13455,7 @@
       </c>
       <c r="E226" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F226" s="46">
         <v>43370</v>
@@ -13039,7 +13476,7 @@
       </c>
       <c r="E227" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F227" s="46">
         <v>43373</v>
@@ -13060,7 +13497,7 @@
       </c>
       <c r="E228" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F228" s="46">
         <v>43370</v>
@@ -13081,7 +13518,7 @@
       </c>
       <c r="E229" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F229" s="46">
         <v>43370</v>
@@ -13102,7 +13539,7 @@
       </c>
       <c r="E230" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F230" s="46">
         <v>43388</v>
@@ -13123,7 +13560,7 @@
       </c>
       <c r="E231" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F231" s="46">
         <v>43370</v>
@@ -13144,7 +13581,7 @@
       </c>
       <c r="E232" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F232" s="46">
         <v>43382</v>
@@ -13165,7 +13602,7 @@
       </c>
       <c r="E233" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F233" s="46">
         <v>43378</v>
@@ -13186,7 +13623,7 @@
       </c>
       <c r="E234" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F234" s="46">
         <v>43370</v>
@@ -13207,7 +13644,7 @@
       </c>
       <c r="E235" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F235" s="46">
         <v>43375</v>
@@ -13228,7 +13665,7 @@
       </c>
       <c r="E236" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F236" s="46">
         <v>43369</v>
@@ -13249,7 +13686,7 @@
       </c>
       <c r="E237" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F237" s="46">
         <v>43370</v>
@@ -13270,7 +13707,7 @@
       </c>
       <c r="E238" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F238" s="46">
         <v>43374</v>
@@ -13291,7 +13728,7 @@
       </c>
       <c r="E239" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F239" s="46">
         <v>43385</v>
@@ -13312,7 +13749,7 @@
       </c>
       <c r="E240" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F240" s="46">
         <v>43386</v>
@@ -13333,7 +13770,7 @@
       </c>
       <c r="E241" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F241" s="46">
         <v>43373</v>
@@ -13354,7 +13791,7 @@
       </c>
       <c r="E242" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F242" s="46">
         <v>43373</v>
@@ -13375,7 +13812,7 @@
       </c>
       <c r="E243" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F243" s="46">
         <v>43386</v>
@@ -13396,7 +13833,7 @@
       </c>
       <c r="E244" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F244" s="46">
         <v>43379</v>
@@ -13417,7 +13854,7 @@
       </c>
       <c r="E245" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F245" s="46">
         <v>43372</v>
@@ -13438,7 +13875,7 @@
       </c>
       <c r="E246" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F246" s="46">
         <v>43369</v>
@@ -13459,7 +13896,7 @@
       </c>
       <c r="E247" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F247" s="46">
         <v>43380</v>
@@ -13480,7 +13917,7 @@
       </c>
       <c r="E248" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F248" s="46">
         <v>43369</v>
@@ -13501,7 +13938,7 @@
       </c>
       <c r="E249" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F249" s="46">
         <v>43377</v>
@@ -13522,7 +13959,7 @@
       </c>
       <c r="E250" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F250" s="46">
         <v>43388</v>
@@ -13543,7 +13980,7 @@
       </c>
       <c r="E251" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F251" s="46">
         <v>43382</v>
@@ -13564,7 +14001,7 @@
       </c>
       <c r="E252" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F252" s="46">
         <v>43380</v>
@@ -13585,7 +14022,7 @@
       </c>
       <c r="E253" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F253" s="46">
         <v>43383</v>
@@ -13606,7 +14043,7 @@
       </c>
       <c r="E254" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F254" s="46">
         <v>43380</v>
@@ -13627,7 +14064,7 @@
       </c>
       <c r="E255" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F255" s="46">
         <v>43369</v>
@@ -13648,7 +14085,7 @@
       </c>
       <c r="E256" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F256" s="46">
         <v>43372</v>
@@ -13669,7 +14106,7 @@
       </c>
       <c r="E257" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F257" s="46">
         <v>43387</v>
@@ -13690,7 +14127,7 @@
       </c>
       <c r="E258" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F258" s="46">
         <v>43384</v>
@@ -13711,7 +14148,7 @@
       </c>
       <c r="E259" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F259" s="46">
         <v>43375</v>
@@ -13732,7 +14169,7 @@
       </c>
       <c r="E260" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F260" s="46">
         <v>43372</v>
@@ -13753,7 +14190,7 @@
       </c>
       <c r="E261" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F261" s="46">
         <v>43379</v>
@@ -13774,7 +14211,7 @@
       </c>
       <c r="E262" s="41">
         <f t="shared" ref="E262:E325" ca="1" si="4">RANDBETWEEN(1,20)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F262" s="46">
         <v>43369</v>
@@ -13795,7 +14232,7 @@
       </c>
       <c r="E263" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F263" s="46">
         <v>43373</v>
@@ -13816,7 +14253,7 @@
       </c>
       <c r="E264" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F264" s="46">
         <v>43384</v>
@@ -13837,7 +14274,7 @@
       </c>
       <c r="E265" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F265" s="46">
         <v>43381</v>
@@ -13858,7 +14295,7 @@
       </c>
       <c r="E266" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F266" s="46">
         <v>43378</v>
@@ -13879,7 +14316,7 @@
       </c>
       <c r="E267" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F267" s="46">
         <v>43379</v>
@@ -13921,7 +14358,7 @@
       </c>
       <c r="E269" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F269" s="46">
         <v>43385</v>
@@ -13942,7 +14379,7 @@
       </c>
       <c r="E270" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F270" s="46">
         <v>43369</v>
@@ -13963,7 +14400,7 @@
       </c>
       <c r="E271" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F271" s="46">
         <v>43388</v>
@@ -13984,7 +14421,7 @@
       </c>
       <c r="E272" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F272" s="46">
         <v>43373</v>
@@ -14005,7 +14442,7 @@
       </c>
       <c r="E273" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F273" s="46">
         <v>43383</v>
@@ -14026,7 +14463,7 @@
       </c>
       <c r="E274" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F274" s="46">
         <v>43375</v>
@@ -14047,7 +14484,7 @@
       </c>
       <c r="E275" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F275" s="46">
         <v>43378</v>
@@ -14068,7 +14505,7 @@
       </c>
       <c r="E276" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F276" s="46">
         <v>43383</v>
@@ -14089,7 +14526,7 @@
       </c>
       <c r="E277" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F277" s="46">
         <v>43373</v>
@@ -14110,7 +14547,7 @@
       </c>
       <c r="E278" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F278" s="46">
         <v>43384</v>
@@ -14131,7 +14568,7 @@
       </c>
       <c r="E279" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F279" s="46">
         <v>43374</v>
@@ -14152,7 +14589,7 @@
       </c>
       <c r="E280" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F280" s="46">
         <v>43379</v>
@@ -14173,7 +14610,7 @@
       </c>
       <c r="E281" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F281" s="46">
         <v>43386</v>
@@ -14194,7 +14631,7 @@
       </c>
       <c r="E282" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F282" s="46">
         <v>43388</v>
@@ -14215,7 +14652,7 @@
       </c>
       <c r="E283" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F283" s="46">
         <v>43379</v>
@@ -14236,7 +14673,7 @@
       </c>
       <c r="E284" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F284" s="46">
         <v>43384</v>
@@ -14257,7 +14694,7 @@
       </c>
       <c r="E285" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F285" s="46">
         <v>43372</v>
@@ -14278,7 +14715,7 @@
       </c>
       <c r="E286" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F286" s="46">
         <v>43384</v>
@@ -14299,7 +14736,7 @@
       </c>
       <c r="E287" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F287" s="46">
         <v>43386</v>
@@ -14320,7 +14757,7 @@
       </c>
       <c r="E288" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F288" s="46">
         <v>43382</v>
@@ -14341,7 +14778,7 @@
       </c>
       <c r="E289" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F289" s="46">
         <v>43383</v>
@@ -14362,7 +14799,7 @@
       </c>
       <c r="E290" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F290" s="46">
         <v>43376</v>
@@ -14383,7 +14820,7 @@
       </c>
       <c r="E291" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F291" s="46">
         <v>43371</v>
@@ -14404,7 +14841,7 @@
       </c>
       <c r="E292" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F292" s="46">
         <v>43386</v>
@@ -14425,7 +14862,7 @@
       </c>
       <c r="E293" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F293" s="46">
         <v>43375</v>
@@ -14446,7 +14883,7 @@
       </c>
       <c r="E294" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F294" s="46">
         <v>43371</v>
@@ -14467,7 +14904,7 @@
       </c>
       <c r="E295" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F295" s="46">
         <v>43387</v>
@@ -14488,7 +14925,7 @@
       </c>
       <c r="E296" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F296" s="46">
         <v>43387</v>
@@ -14509,7 +14946,7 @@
       </c>
       <c r="E297" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F297" s="46">
         <v>43381</v>
@@ -14530,7 +14967,7 @@
       </c>
       <c r="E298" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F298" s="46">
         <v>43371</v>
@@ -14551,7 +14988,7 @@
       </c>
       <c r="E299" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F299" s="46">
         <v>43374</v>
@@ -14572,7 +15009,7 @@
       </c>
       <c r="E300" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F300" s="46">
         <v>43378</v>
@@ -14593,7 +15030,7 @@
       </c>
       <c r="E301" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F301" s="46">
         <v>43378</v>
@@ -14614,7 +15051,7 @@
       </c>
       <c r="E302" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F302" s="46">
         <v>43381</v>
@@ -14635,7 +15072,7 @@
       </c>
       <c r="E303" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F303" s="46">
         <v>43384</v>
@@ -14656,7 +15093,7 @@
       </c>
       <c r="E304" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F304" s="46">
         <v>43371</v>
@@ -14677,7 +15114,7 @@
       </c>
       <c r="E305" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F305" s="46">
         <v>43383</v>
@@ -14698,7 +15135,7 @@
       </c>
       <c r="E306" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F306" s="46">
         <v>43375</v>
@@ -14719,7 +15156,7 @@
       </c>
       <c r="E307" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F307" s="46">
         <v>43387</v>
@@ -14740,7 +15177,7 @@
       </c>
       <c r="E308" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F308" s="46">
         <v>43387</v>
@@ -14761,7 +15198,7 @@
       </c>
       <c r="E309" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F309" s="46">
         <v>43370</v>
@@ -14782,7 +15219,7 @@
       </c>
       <c r="E310" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F310" s="46">
         <v>43369</v>
@@ -14803,7 +15240,7 @@
       </c>
       <c r="E311" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F311" s="46">
         <v>43388</v>
@@ -14824,7 +15261,7 @@
       </c>
       <c r="E312" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F312" s="46">
         <v>43387</v>
@@ -14845,7 +15282,7 @@
       </c>
       <c r="E313" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F313" s="46">
         <v>43381</v>
@@ -14887,7 +15324,7 @@
       </c>
       <c r="E315" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F315" s="46">
         <v>43373</v>
@@ -14908,7 +15345,7 @@
       </c>
       <c r="E316" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F316" s="46">
         <v>43382</v>
@@ -14929,7 +15366,7 @@
       </c>
       <c r="E317" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F317" s="46">
         <v>43370</v>
@@ -14950,7 +15387,7 @@
       </c>
       <c r="E318" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F318" s="46">
         <v>43376</v>
@@ -14971,7 +15408,7 @@
       </c>
       <c r="E319" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F319" s="46">
         <v>43377</v>
@@ -14992,7 +15429,7 @@
       </c>
       <c r="E320" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F320" s="46">
         <v>43375</v>
@@ -15013,7 +15450,7 @@
       </c>
       <c r="E321" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F321" s="46">
         <v>43377</v>
@@ -15034,7 +15471,7 @@
       </c>
       <c r="E322" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F322" s="46">
         <v>43380</v>
@@ -15055,7 +15492,7 @@
       </c>
       <c r="E323" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F323" s="46">
         <v>43372</v>
@@ -15076,7 +15513,7 @@
       </c>
       <c r="E324" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F324" s="46">
         <v>43384</v>
@@ -15097,7 +15534,7 @@
       </c>
       <c r="E325" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F325" s="46">
         <v>43370</v>
@@ -15118,7 +15555,7 @@
       </c>
       <c r="E326" s="41">
         <f t="shared" ref="E326:E389" ca="1" si="5">RANDBETWEEN(1,20)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F326" s="46">
         <v>43381</v>
@@ -15139,7 +15576,7 @@
       </c>
       <c r="E327" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F327" s="46">
         <v>43388</v>
@@ -15160,7 +15597,7 @@
       </c>
       <c r="E328" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F328" s="46">
         <v>43373</v>
@@ -15181,7 +15618,7 @@
       </c>
       <c r="E329" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F329" s="46">
         <v>43384</v>
@@ -15202,7 +15639,7 @@
       </c>
       <c r="E330" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F330" s="46">
         <v>43387</v>
@@ -15223,7 +15660,7 @@
       </c>
       <c r="E331" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F331" s="46">
         <v>43382</v>
@@ -15244,7 +15681,7 @@
       </c>
       <c r="E332" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F332" s="46">
         <v>43373</v>
@@ -15265,7 +15702,7 @@
       </c>
       <c r="E333" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F333" s="46">
         <v>43376</v>
@@ -15286,7 +15723,7 @@
       </c>
       <c r="E334" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F334" s="46">
         <v>43386</v>
@@ -15307,7 +15744,7 @@
       </c>
       <c r="E335" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F335" s="46">
         <v>43380</v>
@@ -15328,7 +15765,7 @@
       </c>
       <c r="E336" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F336" s="46">
         <v>43376</v>
@@ -15349,7 +15786,7 @@
       </c>
       <c r="E337" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F337" s="46">
         <v>43377</v>
@@ -15370,7 +15807,7 @@
       </c>
       <c r="E338" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F338" s="46">
         <v>43380</v>
@@ -15391,7 +15828,7 @@
       </c>
       <c r="E339" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F339" s="46">
         <v>43387</v>
@@ -15412,7 +15849,7 @@
       </c>
       <c r="E340" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F340" s="46">
         <v>43373</v>
@@ -15433,7 +15870,7 @@
       </c>
       <c r="E341" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F341" s="46">
         <v>43379</v>
@@ -15454,7 +15891,7 @@
       </c>
       <c r="E342" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F342" s="46">
         <v>43371</v>
@@ -15496,7 +15933,7 @@
       </c>
       <c r="E344" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F344" s="46">
         <v>43382</v>
@@ -15517,7 +15954,7 @@
       </c>
       <c r="E345" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F345" s="46">
         <v>43370</v>
@@ -15538,7 +15975,7 @@
       </c>
       <c r="E346" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F346" s="46">
         <v>43370</v>
@@ -15559,7 +15996,7 @@
       </c>
       <c r="E347" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F347" s="46">
         <v>43380</v>
@@ -15580,7 +16017,7 @@
       </c>
       <c r="E348" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F348" s="46">
         <v>43382</v>
@@ -15601,7 +16038,7 @@
       </c>
       <c r="E349" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F349" s="46">
         <v>43376</v>
@@ -15622,7 +16059,7 @@
       </c>
       <c r="E350" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F350" s="46">
         <v>43369</v>
@@ -15643,7 +16080,7 @@
       </c>
       <c r="E351" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F351" s="46">
         <v>43377</v>
@@ -15664,7 +16101,7 @@
       </c>
       <c r="E352" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F352" s="46">
         <v>43383</v>
@@ -15685,7 +16122,7 @@
       </c>
       <c r="E353" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F353" s="46">
         <v>43375</v>
@@ -15706,7 +16143,7 @@
       </c>
       <c r="E354" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F354" s="46">
         <v>43383</v>
@@ -15727,7 +16164,7 @@
       </c>
       <c r="E355" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F355" s="46">
         <v>43371</v>
@@ -15748,7 +16185,7 @@
       </c>
       <c r="E356" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F356" s="46">
         <v>43369</v>
@@ -15769,7 +16206,7 @@
       </c>
       <c r="E357" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F357" s="46">
         <v>43376</v>
@@ -15790,7 +16227,7 @@
       </c>
       <c r="E358" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F358" s="46">
         <v>43375</v>
@@ -15811,7 +16248,7 @@
       </c>
       <c r="E359" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F359" s="46">
         <v>43382</v>
@@ -15832,7 +16269,7 @@
       </c>
       <c r="E360" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F360" s="46">
         <v>43374</v>
@@ -15853,7 +16290,7 @@
       </c>
       <c r="E361" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F361" s="46">
         <v>43386</v>
@@ -15874,7 +16311,7 @@
       </c>
       <c r="E362" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F362" s="46">
         <v>43384</v>
@@ -15895,7 +16332,7 @@
       </c>
       <c r="E363" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F363" s="46">
         <v>43387</v>
@@ -15916,7 +16353,7 @@
       </c>
       <c r="E364" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F364" s="46">
         <v>43375</v>
@@ -15937,7 +16374,7 @@
       </c>
       <c r="E365" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F365" s="46">
         <v>43386</v>
@@ -15958,7 +16395,7 @@
       </c>
       <c r="E366" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F366" s="46">
         <v>43377</v>
@@ -15979,7 +16416,7 @@
       </c>
       <c r="E367" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F367" s="46">
         <v>43375</v>
@@ -16000,7 +16437,7 @@
       </c>
       <c r="E368" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F368" s="46">
         <v>43380</v>
@@ -16021,7 +16458,7 @@
       </c>
       <c r="E369" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F369" s="46">
         <v>43378</v>
@@ -16042,7 +16479,7 @@
       </c>
       <c r="E370" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F370" s="46">
         <v>43374</v>
@@ -16063,7 +16500,7 @@
       </c>
       <c r="E371" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F371" s="46">
         <v>43385</v>
@@ -16084,7 +16521,7 @@
       </c>
       <c r="E372" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F372" s="46">
         <v>43377</v>
@@ -16105,7 +16542,7 @@
       </c>
       <c r="E373" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F373" s="46">
         <v>43378</v>
@@ -16126,7 +16563,7 @@
       </c>
       <c r="E374" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F374" s="46">
         <v>43381</v>
@@ -16147,7 +16584,7 @@
       </c>
       <c r="E375" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F375" s="46">
         <v>43387</v>
@@ -16168,7 +16605,7 @@
       </c>
       <c r="E376" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F376" s="46">
         <v>43378</v>
@@ -16189,7 +16626,7 @@
       </c>
       <c r="E377" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F377" s="46">
         <v>43370</v>
@@ -16210,7 +16647,7 @@
       </c>
       <c r="E378" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F378" s="46">
         <v>43372</v>
@@ -16231,7 +16668,7 @@
       </c>
       <c r="E379" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F379" s="46">
         <v>43386</v>
@@ -16252,7 +16689,7 @@
       </c>
       <c r="E380" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F380" s="46">
         <v>43383</v>
@@ -16273,7 +16710,7 @@
       </c>
       <c r="E381" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F381" s="46">
         <v>43386</v>
@@ -16294,7 +16731,7 @@
       </c>
       <c r="E382" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F382" s="46">
         <v>43379</v>
@@ -16315,7 +16752,7 @@
       </c>
       <c r="E383" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F383" s="46">
         <v>43369</v>
@@ -16336,7 +16773,7 @@
       </c>
       <c r="E384" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F384" s="46">
         <v>43371</v>
@@ -16357,7 +16794,7 @@
       </c>
       <c r="E385" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F385" s="46">
         <v>43370</v>
@@ -16378,7 +16815,7 @@
       </c>
       <c r="E386" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F386" s="46">
         <v>43370</v>
@@ -16399,7 +16836,7 @@
       </c>
       <c r="E387" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F387" s="46">
         <v>43384</v>
@@ -16420,7 +16857,7 @@
       </c>
       <c r="E388" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F388" s="46">
         <v>43386</v>
@@ -16441,7 +16878,7 @@
       </c>
       <c r="E389" s="41">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F389" s="46">
         <v>43370</v>
@@ -16462,7 +16899,7 @@
       </c>
       <c r="E390" s="41">
         <f t="shared" ref="E390:E453" ca="1" si="6">RANDBETWEEN(1,20)</f>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F390" s="46">
         <v>43384</v>
@@ -16483,7 +16920,7 @@
       </c>
       <c r="E391" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F391" s="46">
         <v>43378</v>
@@ -16504,7 +16941,7 @@
       </c>
       <c r="E392" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F392" s="46">
         <v>43379</v>
@@ -16525,7 +16962,7 @@
       </c>
       <c r="E393" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F393" s="46">
         <v>43385</v>
@@ -16546,7 +16983,7 @@
       </c>
       <c r="E394" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F394" s="46">
         <v>43379</v>
@@ -16567,7 +17004,7 @@
       </c>
       <c r="E395" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F395" s="46">
         <v>43384</v>
@@ -16588,7 +17025,7 @@
       </c>
       <c r="E396" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F396" s="46">
         <v>43376</v>
@@ -16630,7 +17067,7 @@
       </c>
       <c r="E398" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F398" s="46">
         <v>43380</v>
@@ -16651,7 +17088,7 @@
       </c>
       <c r="E399" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F399" s="46">
         <v>43371</v>
@@ -16672,7 +17109,7 @@
       </c>
       <c r="E400" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F400" s="46">
         <v>43375</v>
@@ -16693,7 +17130,7 @@
       </c>
       <c r="E401" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F401" s="46">
         <v>43370</v>
@@ -16714,7 +17151,7 @@
       </c>
       <c r="E402" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F402" s="46">
         <v>43371</v>
@@ -16735,7 +17172,7 @@
       </c>
       <c r="E403" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F403" s="46">
         <v>43371</v>
@@ -16756,7 +17193,7 @@
       </c>
       <c r="E404" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F404" s="46">
         <v>43383</v>
@@ -16777,7 +17214,7 @@
       </c>
       <c r="E405" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F405" s="46">
         <v>43386</v>
@@ -16798,7 +17235,7 @@
       </c>
       <c r="E406" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F406" s="46">
         <v>43387</v>
@@ -16819,7 +17256,7 @@
       </c>
       <c r="E407" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F407" s="46">
         <v>43379</v>
@@ -16840,7 +17277,7 @@
       </c>
       <c r="E408" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F408" s="46">
         <v>43378</v>
@@ -16861,7 +17298,7 @@
       </c>
       <c r="E409" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F409" s="46">
         <v>43386</v>
@@ -16882,7 +17319,7 @@
       </c>
       <c r="E410" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F410" s="46">
         <v>43382</v>
@@ -16903,7 +17340,7 @@
       </c>
       <c r="E411" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F411" s="46">
         <v>43372</v>
@@ -16924,7 +17361,7 @@
       </c>
       <c r="E412" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F412" s="46">
         <v>43388</v>
@@ -16945,7 +17382,7 @@
       </c>
       <c r="E413" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F413" s="46">
         <v>43370</v>
@@ -16987,7 +17424,7 @@
       </c>
       <c r="E415" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F415" s="46">
         <v>43375</v>
@@ -17008,7 +17445,7 @@
       </c>
       <c r="E416" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F416" s="46">
         <v>43370</v>
@@ -17029,7 +17466,7 @@
       </c>
       <c r="E417" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F417" s="46">
         <v>43387</v>
@@ -17050,7 +17487,7 @@
       </c>
       <c r="E418" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F418" s="46">
         <v>43371</v>
@@ -17071,7 +17508,7 @@
       </c>
       <c r="E419" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F419" s="46">
         <v>43372</v>
@@ -17092,7 +17529,7 @@
       </c>
       <c r="E420" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F420" s="46">
         <v>43374</v>
@@ -17113,7 +17550,7 @@
       </c>
       <c r="E421" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F421" s="46">
         <v>43375</v>
@@ -17134,7 +17571,7 @@
       </c>
       <c r="E422" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F422" s="46">
         <v>43378</v>
@@ -17176,7 +17613,7 @@
       </c>
       <c r="E424" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F424" s="46">
         <v>43384</v>
@@ -17197,7 +17634,7 @@
       </c>
       <c r="E425" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F425" s="46">
         <v>43383</v>
@@ -17218,7 +17655,7 @@
       </c>
       <c r="E426" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F426" s="46">
         <v>43388</v>
@@ -17239,7 +17676,7 @@
       </c>
       <c r="E427" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F427" s="46">
         <v>43372</v>
@@ -17260,7 +17697,7 @@
       </c>
       <c r="E428" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F428" s="46">
         <v>43377</v>
@@ -17281,7 +17718,7 @@
       </c>
       <c r="E429" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F429" s="46">
         <v>43374</v>
@@ -17302,7 +17739,7 @@
       </c>
       <c r="E430" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F430" s="46">
         <v>43378</v>
@@ -17323,7 +17760,7 @@
       </c>
       <c r="E431" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F431" s="46">
         <v>43379</v>
@@ -17344,7 +17781,7 @@
       </c>
       <c r="E432" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F432" s="46">
         <v>43384</v>
@@ -17365,7 +17802,7 @@
       </c>
       <c r="E433" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F433" s="46">
         <v>43387</v>
@@ -17386,7 +17823,7 @@
       </c>
       <c r="E434" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F434" s="46">
         <v>43376</v>
@@ -17407,7 +17844,7 @@
       </c>
       <c r="E435" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F435" s="46">
         <v>43385</v>
@@ -17428,7 +17865,7 @@
       </c>
       <c r="E436" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F436" s="46">
         <v>43374</v>
@@ -17449,7 +17886,7 @@
       </c>
       <c r="E437" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F437" s="46">
         <v>43376</v>
@@ -17470,7 +17907,7 @@
       </c>
       <c r="E438" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F438" s="46">
         <v>43370</v>
@@ -17491,7 +17928,7 @@
       </c>
       <c r="E439" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F439" s="46">
         <v>43370</v>
@@ -17512,7 +17949,7 @@
       </c>
       <c r="E440" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F440" s="46">
         <v>43385</v>
@@ -17533,7 +17970,7 @@
       </c>
       <c r="E441" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F441" s="46">
         <v>43370</v>
@@ -17554,7 +17991,7 @@
       </c>
       <c r="E442" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F442" s="46">
         <v>43374</v>
@@ -17575,7 +18012,7 @@
       </c>
       <c r="E443" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F443" s="46">
         <v>43369</v>
@@ -17596,7 +18033,7 @@
       </c>
       <c r="E444" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F444" s="46">
         <v>43385</v>
@@ -17617,7 +18054,7 @@
       </c>
       <c r="E445" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F445" s="46">
         <v>43379</v>
@@ -17638,7 +18075,7 @@
       </c>
       <c r="E446" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F446" s="46">
         <v>43371</v>
@@ -17659,7 +18096,7 @@
       </c>
       <c r="E447" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F447" s="46">
         <v>43372</v>
@@ -17680,7 +18117,7 @@
       </c>
       <c r="E448" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F448" s="46">
         <v>43378</v>
@@ -17701,7 +18138,7 @@
       </c>
       <c r="E449" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F449" s="46">
         <v>43384</v>
@@ -17722,7 +18159,7 @@
       </c>
       <c r="E450" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F450" s="46">
         <v>43380</v>
@@ -17743,7 +18180,7 @@
       </c>
       <c r="E451" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F451" s="46">
         <v>43374</v>
@@ -17764,7 +18201,7 @@
       </c>
       <c r="E452" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F452" s="46">
         <v>43372</v>
@@ -17785,7 +18222,7 @@
       </c>
       <c r="E453" s="41">
         <f t="shared" ca="1" si="6"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F453" s="46">
         <v>43376</v>
@@ -17806,7 +18243,7 @@
       </c>
       <c r="E454" s="41">
         <f t="shared" ref="E454:E517" ca="1" si="7">RANDBETWEEN(1,20)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F454" s="46">
         <v>43369</v>
@@ -17827,7 +18264,7 @@
       </c>
       <c r="E455" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F455" s="46">
         <v>43374</v>
@@ -17848,7 +18285,7 @@
       </c>
       <c r="E456" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F456" s="46">
         <v>43371</v>
@@ -17869,7 +18306,7 @@
       </c>
       <c r="E457" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F457" s="46">
         <v>43373</v>
@@ -17890,7 +18327,7 @@
       </c>
       <c r="E458" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F458" s="46">
         <v>43380</v>
@@ -17911,7 +18348,7 @@
       </c>
       <c r="E459" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F459" s="46">
         <v>43381</v>
@@ -17932,7 +18369,7 @@
       </c>
       <c r="E460" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F460" s="46">
         <v>43372</v>
@@ -17953,7 +18390,7 @@
       </c>
       <c r="E461" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F461" s="46">
         <v>43382</v>
@@ -17974,7 +18411,7 @@
       </c>
       <c r="E462" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F462" s="46">
         <v>43380</v>
@@ -18016,7 +18453,7 @@
       </c>
       <c r="E464" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F464" s="46">
         <v>43374</v>
@@ -18037,7 +18474,7 @@
       </c>
       <c r="E465" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F465" s="46">
         <v>43378</v>
@@ -18058,7 +18495,7 @@
       </c>
       <c r="E466" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F466" s="46">
         <v>43375</v>
@@ -18079,7 +18516,7 @@
       </c>
       <c r="E467" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F467" s="46">
         <v>43380</v>
@@ -18100,7 +18537,7 @@
       </c>
       <c r="E468" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F468" s="46">
         <v>43373</v>
@@ -18121,7 +18558,7 @@
       </c>
       <c r="E469" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F469" s="46">
         <v>43372</v>
@@ -18142,7 +18579,7 @@
       </c>
       <c r="E470" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F470" s="46">
         <v>43371</v>
@@ -18163,7 +18600,7 @@
       </c>
       <c r="E471" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F471" s="46">
         <v>43374</v>
@@ -18184,7 +18621,7 @@
       </c>
       <c r="E472" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F472" s="46">
         <v>43386</v>
@@ -18205,7 +18642,7 @@
       </c>
       <c r="E473" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F473" s="46">
         <v>43378</v>
@@ -18226,7 +18663,7 @@
       </c>
       <c r="E474" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F474" s="46">
         <v>43388</v>
@@ -18247,7 +18684,7 @@
       </c>
       <c r="E475" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F475" s="46">
         <v>43376</v>
@@ -18268,7 +18705,7 @@
       </c>
       <c r="E476" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F476" s="46">
         <v>43375</v>
@@ -18289,7 +18726,7 @@
       </c>
       <c r="E477" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F477" s="46">
         <v>43381</v>
@@ -18310,7 +18747,7 @@
       </c>
       <c r="E478" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F478" s="46">
         <v>43374</v>
@@ -18331,7 +18768,7 @@
       </c>
       <c r="E479" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F479" s="46">
         <v>43374</v>
@@ -18352,7 +18789,7 @@
       </c>
       <c r="E480" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F480" s="46">
         <v>43386</v>
@@ -18373,7 +18810,7 @@
       </c>
       <c r="E481" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F481" s="46">
         <v>43386</v>
@@ -18394,7 +18831,7 @@
       </c>
       <c r="E482" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F482" s="46">
         <v>43375</v>
@@ -18415,7 +18852,7 @@
       </c>
       <c r="E483" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F483" s="46">
         <v>43382</v>
@@ -18436,7 +18873,7 @@
       </c>
       <c r="E484" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F484" s="46">
         <v>43380</v>
@@ -18457,7 +18894,7 @@
       </c>
       <c r="E485" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F485" s="46">
         <v>43370</v>
@@ -18478,7 +18915,7 @@
       </c>
       <c r="E486" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F486" s="46">
         <v>43376</v>
@@ -18499,7 +18936,7 @@
       </c>
       <c r="E487" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F487" s="46">
         <v>43372</v>
@@ -18520,7 +18957,7 @@
       </c>
       <c r="E488" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F488" s="46">
         <v>43371</v>
@@ -18541,7 +18978,7 @@
       </c>
       <c r="E489" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F489" s="46">
         <v>43381</v>
@@ -18562,7 +18999,7 @@
       </c>
       <c r="E490" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F490" s="46">
         <v>43369</v>
@@ -18583,7 +19020,7 @@
       </c>
       <c r="E491" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F491" s="46">
         <v>43381</v>
@@ -18604,7 +19041,7 @@
       </c>
       <c r="E492" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F492" s="46">
         <v>43377</v>
@@ -18625,7 +19062,7 @@
       </c>
       <c r="E493" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F493" s="46">
         <v>43372</v>
@@ -18646,7 +19083,7 @@
       </c>
       <c r="E494" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F494" s="46">
         <v>43384</v>
@@ -18667,7 +19104,7 @@
       </c>
       <c r="E495" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F495" s="46">
         <v>43373</v>
@@ -18688,7 +19125,7 @@
       </c>
       <c r="E496" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F496" s="46">
         <v>43374</v>
@@ -18709,7 +19146,7 @@
       </c>
       <c r="E497" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F497" s="46">
         <v>43384</v>
@@ -18730,7 +19167,7 @@
       </c>
       <c r="E498" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F498" s="46">
         <v>43370</v>
@@ -18751,7 +19188,7 @@
       </c>
       <c r="E499" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F499" s="46">
         <v>43375</v>
@@ -18772,7 +19209,7 @@
       </c>
       <c r="E500" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F500" s="46">
         <v>43374</v>
@@ -18793,7 +19230,7 @@
       </c>
       <c r="E501" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F501" s="46">
         <v>43388</v>
@@ -18814,7 +19251,7 @@
       </c>
       <c r="E502" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F502" s="46">
         <v>43387</v>
@@ -18835,7 +19272,7 @@
       </c>
       <c r="E503" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F503" s="46">
         <v>43373</v>
@@ -18856,7 +19293,7 @@
       </c>
       <c r="E504" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F504" s="46">
         <v>43369</v>
@@ -18877,7 +19314,7 @@
       </c>
       <c r="E505" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F505" s="46">
         <v>43379</v>
@@ -18898,7 +19335,7 @@
       </c>
       <c r="E506" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F506" s="46">
         <v>43385</v>
@@ -18919,7 +19356,7 @@
       </c>
       <c r="E507" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F507" s="46">
         <v>43376</v>
@@ -18940,7 +19377,7 @@
       </c>
       <c r="E508" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F508" s="46">
         <v>43371</v>
@@ -18961,7 +19398,7 @@
       </c>
       <c r="E509" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F509" s="46">
         <v>43371</v>
@@ -18982,7 +19419,7 @@
       </c>
       <c r="E510" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F510" s="46">
         <v>43388</v>
@@ -19003,7 +19440,7 @@
       </c>
       <c r="E511" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F511" s="46">
         <v>43375</v>
@@ -19024,7 +19461,7 @@
       </c>
       <c r="E512" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F512" s="46">
         <v>43378</v>
@@ -19045,7 +19482,7 @@
       </c>
       <c r="E513" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F513" s="46">
         <v>43383</v>
@@ -19066,7 +19503,7 @@
       </c>
       <c r="E514" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F514" s="46">
         <v>43374</v>
@@ -19087,7 +19524,7 @@
       </c>
       <c r="E515" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F515" s="46">
         <v>43375</v>
@@ -19108,7 +19545,7 @@
       </c>
       <c r="E516" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F516" s="46">
         <v>43374</v>
@@ -19129,7 +19566,7 @@
       </c>
       <c r="E517" s="41">
         <f t="shared" ca="1" si="7"/>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F517" s="46">
         <v>43385</v>
@@ -19150,7 +19587,7 @@
       </c>
       <c r="E518" s="41">
         <f t="shared" ref="E518:E532" ca="1" si="8">RANDBETWEEN(1,20)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F518" s="46">
         <v>43370</v>
@@ -19171,7 +19608,7 @@
       </c>
       <c r="E519" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F519" s="46">
         <v>43380</v>
@@ -19192,7 +19629,7 @@
       </c>
       <c r="E520" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F520" s="46">
         <v>43378</v>
@@ -19213,7 +19650,7 @@
       </c>
       <c r="E521" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F521" s="46">
         <v>43376</v>
@@ -19234,7 +19671,7 @@
       </c>
       <c r="E522" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F522" s="46">
         <v>43373</v>
@@ -19255,7 +19692,7 @@
       </c>
       <c r="E523" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F523" s="46">
         <v>43370</v>
@@ -19276,7 +19713,7 @@
       </c>
       <c r="E524" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F524" s="46">
         <v>43387</v>
@@ -19297,7 +19734,7 @@
       </c>
       <c r="E525" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F525" s="46">
         <v>43369</v>
@@ -19318,7 +19755,7 @@
       </c>
       <c r="E526" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F526" s="46">
         <v>43376</v>
@@ -19339,7 +19776,7 @@
       </c>
       <c r="E527" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F527" s="46">
         <v>43371</v>
@@ -19360,7 +19797,7 @@
       </c>
       <c r="E528" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F528" s="46">
         <v>43382</v>
@@ -19381,7 +19818,7 @@
       </c>
       <c r="E529" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F529" s="46">
         <v>43370</v>
@@ -19402,7 +19839,7 @@
       </c>
       <c r="E530" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F530" s="46">
         <v>43374</v>
@@ -19423,7 +19860,7 @@
       </c>
       <c r="E531" s="41">
         <f t="shared" ca="1" si="8"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F531" s="46">
         <v>43370</v>
